--- a/employee_incident_report_forms/004_threat_assessment_form--employee_incident_report_forms.xlsx
+++ b/employee_incident_report_forms/004_threat_assessment_form--employee_incident_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'critical'}</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Critical'}</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cyber_threat'}</t>
+          <t>cyber_threat</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cyber Threat'}</t>
+          <t>Cyber Threat</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'physical_threat'}</t>
+          <t>physical_threat</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Physical Threat'}</t>
+          <t>Physical Threat</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'human_threat'}</t>
+          <t>human_threat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Human Threat'}</t>
+          <t>Human Threat</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'network'}</t>
+          <t>network</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Network'}</t>
+          <t>Network</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'system'}</t>
+          <t>system</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'System'}</t>
+          <t>System</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'physical'}</t>
+          <t>physical</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Physical'}</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'network'}</t>
+          <t>network</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Network'}</t>
+          <t>Network</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'system'}</t>
+          <t>system</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'System'}</t>
+          <t>System</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'physical'}</t>
+          <t>physical</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Physical'}</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'network'}</t>
+          <t>network</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Network'}</t>
+          <t>Network</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'system'}</t>
+          <t>system</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'System'}</t>
+          <t>System</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'physical'}</t>
+          <t>physical</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Physical'}</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
